--- a/artfynd/S 1108-2025 artfynd.xlsx
+++ b/artfynd/S 1108-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724818</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232558</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724797</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724798</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724830</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724831</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724832</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724833</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724834</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1855,6 +1915,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724901</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1952,6 +2017,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724796</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724846</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2146,6 +2221,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724847</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2243,6 +2323,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724848</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2340,6 +2425,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724849</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2437,6 +2527,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,6 +2629,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724851</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2631,6 +2731,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724852</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2728,6 +2833,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724853</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2825,6 +2935,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724854</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2922,6 +3037,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724855</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3019,6 +3139,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724856</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3116,6 +3241,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724857</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3213,6 +3343,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724858</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3310,6 +3445,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724859</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3407,6 +3547,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724860</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3504,6 +3649,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724861</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3601,6 +3751,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3698,6 +3853,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724863</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3795,6 +3955,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724864</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3892,6 +4057,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724865</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3989,6 +4159,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724866</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4086,6 +4261,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724867</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4183,6 +4363,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724868</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4280,6 +4465,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724869</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4377,6 +4567,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724871</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4474,6 +4669,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724872</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4571,6 +4771,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724874</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4668,6 +4873,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724875</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4765,6 +4975,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724876</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4862,6 +5077,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724877</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4959,6 +5179,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724878</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5056,6 +5281,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724879</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5153,6 +5383,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724881</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5250,6 +5485,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724882</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5347,6 +5587,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724883</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5444,6 +5689,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724884</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5541,6 +5791,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724885</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5638,6 +5893,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724886</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5735,6 +5995,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724887</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5832,6 +6097,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724888</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5929,6 +6199,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724889</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6026,6 +6301,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724890</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6123,6 +6403,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724891</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6220,6 +6505,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724892</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6317,6 +6607,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724893</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6414,6 +6709,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724894</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6511,6 +6811,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724895</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6608,6 +6913,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724896</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6705,6 +7015,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724897</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6802,6 +7117,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724898</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6903,6 +7223,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232565</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7000,6 +7325,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724820</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7097,6 +7427,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724822</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7194,6 +7529,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724823</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7291,6 +7631,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724825</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7388,6 +7733,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724826</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7489,6 +7839,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232526</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7586,6 +7941,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724801</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7685,6 +8045,11 @@
       <c r="AY73" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232550</t>
         </is>
       </c>
     </row>
@@ -7807,6 +8172,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232486</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7923,6 +8293,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232557</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8020,6 +8395,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724838</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8117,6 +8497,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724839</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8214,6 +8599,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724840</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8311,6 +8701,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724841</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8412,6 +8807,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232559</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8509,6 +8909,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724828</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8606,6 +9011,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724800</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8703,6 +9113,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724835</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8800,6 +9215,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724836</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8897,8 +9317,99 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120724837</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>